--- a/data/b2_primavera/B2 Primavera 10-2025.xlsx
+++ b/data/b2_primavera/B2 Primavera 10-2025.xlsx
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>57553.75</v>
+        <v>56997.3</v>
       </c>
     </row>
     <row r="3">
@@ -4882,25 +4882,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2718.71</v>
+        <v>2678.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45940</v>
+        <v>45936</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>14000</v>
+        <v>5134.08</v>
       </c>
     </row>
     <row r="5">
@@ -4909,34 +4909,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>45942</v>
+        <v>45940</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3696.26</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
@@ -4945,52 +4945,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1270.9</v>
+        <v>3915.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>776.01</v>
+        <v>1302.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45945</v>
+        <v>45943</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8949.940000000001</v>
+        <v>1243.89</v>
       </c>
     </row>
     <row r="10">
@@ -4999,70 +4999,70 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1820.43</v>
+        <v>9348.030000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45948</v>
+        <v>45945</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1134.11</v>
+        <v>1403.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45949</v>
+        <v>45948</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3867.92</v>
+        <v>1576.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45950</v>
+        <v>45949</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20259.8</v>
+        <v>3793.04</v>
       </c>
     </row>
     <row r="14">
@@ -5071,21 +5071,21 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1425.23</v>
+        <v>20430.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45954</v>
+        <v>45950</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5094,29 +5094,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2456.5</v>
+        <v>2419.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45956</v>
+        <v>45950</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3448.51</v>
+        <v>1555.3</v>
       </c>
     </row>
     <row r="17">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3893.98</v>
+        <v>3660.7</v>
       </c>
     </row>
     <row r="18">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2986.58</v>
+        <v>2694.69</v>
       </c>
     </row>
   </sheetData>
